--- a/sample_data/事件_示例.xlsx
+++ b/sample_data/事件_示例.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,458 +430,610 @@
   </sheetPr>
   <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>事件名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>事件内容</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>事件发生时间</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>上头条热榜时间</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>下头条热榜时间</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>事件结束时间</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>评论信息</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>图片</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>是否为虚假</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>1小时</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>2小时</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>4小时</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>6小时</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>8小时</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>10小时</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>12小时</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>18小时</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>24小时</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>36小时</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>48小时</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>96小时</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="101.5" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>今日亚运将决出18枚金牌</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>【#中国队亚运今日看点#】#今日亚运将决出18枚金牌# 08:30 铁人三项混合接力决赛 林鑫瑜、杨一凡、张玺瑞、李明旭08:45 射击10米气步枪男子团体 盛李豪、张常鸿、马思涵10:00 女子曲棍球小组赛 中国VS中国台北11:30 射击10米气步枪男子个人 盛李豪、张常鸿、马思涵13:30 竞技体操男子个人全能决赛（第二组）张博恒、邹敬园、兰星宇、孙炜、田昊13:30 武术男子太极拳太极剑全能 刘德文15:00 女足小组赛 中国VS菲律宾15:00 女排半决赛 中国VS泰国15:05 女子水球循环赛 中国VS泰国15:50 女子空手道61公斤级、68公斤级决赛 龚莉、李巧巧16:00 多项游泳决赛17:30 男子棒球小组赛 中国vs日本18:00 女篮小组赛 中国vs印尼18:30 男子手球小组赛 中国vs卡塔尔（咪咕体育）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>人民日报</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 07:22:21</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 09:01:20</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="43.5" customHeight="1">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>许嵩 冯禧</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>冯禧的中传研究生毕业记录，她和孙乐言冯琳沈倩是同班同学，又会跳舞又会主持，这时候的她应该想到了自己的事业前景会很好，但她应该没想到自己会和偶像许嵩结婚吧～#一分钟精选视频扶持计划##微博二创视频创作季# 嫂子妹 小C带你瘦的微博视频</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>小C带你瘦</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 00:09:09</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:54:20</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>艺人</t>
         </is>
       </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="72.5" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>罗永浩拒绝透露踩坑餐厅店名</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>【#罗永浩称点6份外卖3份是臭的#】#罗永浩拒绝透露踩坑餐厅店名#9月20日晚，@罗永浩的十字路口 发微博称：“出差和团队一起在深圳赶一个项目，夜里加班点外卖，点到一家在福田区就有两家分店的港式茶餐厅（大众点评两千多条评论分别打了4.6和4.3；2026年必点榜上榜餐厅），结果送过来六份外卖，竟然三份都有异味臭味。这家茶餐厅的名字是……嗯，好吧，都不容易。”评论区有网友询问店名，罗永浩回复：想都不要想！（每经）</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>每日经济新闻</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 22:48:34</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:52:20</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="261" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>果葡糖浆跟水果完全没关系</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>【#果葡糖浆跟水果完全没关系#】#为什么果葡糖浆不比白砂糖更健康# 随着健康观念的普及，人们已经开始有意识地避开一些含有添加糖的食物了，比如配料表中有白砂糖、蔗糖的食物，却在不知不觉中又踩了另一个雷，那就是配料表中带有“果葡糖浆”的食物。我们平常喝的碳酸饮料，吃的糖果、巧克力、蛋糕、饼干、面包等食物里，都能看到果葡糖浆的影子，但很多人都忽略了这个隐藏的“健康刺客”。 果葡糖浆并不是从水果中提取的，而是从玉米淀粉中提取，再经过深加工的化学品。其主要成分是游离态的果糖和葡萄糖，果糖含量可达42%～90%。它可以提供甜味，但没有任何营养价值。为什么果葡糖浆不比白砂糖更健康？首先，二者代谢路径不同：果糖“绕过”了身体的刹车系统。白砂糖（蔗糖）进入体内后会被分解为葡萄糖和果糖，其中的葡萄糖会刺激胰岛素分泌，向身体发出“糖来了”的信号，进而产生饱腹感、调节能量代谢。而果葡糖浆中的果糖是游离状态，几乎全部由肝脏直接代谢，不依赖胰岛素，也不怎么刺激瘦素分泌。这意味着：吃白砂糖，身体有“刹车”；吃果葡糖浆，身体容易“不知不觉吃多”。其次，果葡糖浆对肝脏负担更重，脂肪肝风险更高。由于果糖几乎全靠肝脏处理，过量摄入时肝脏来不及代谢，多余部分会转化为甘油三酯堆积在肝细胞中。台大医院健康电子报的文章解释，食入过多果葡糖浆时，反而容易在肝脏中转成三酸甘油脂，堆积形成脂肪肝；其中间产物“腺嘌呤”还会代谢成尿酸，堆积在关节形成痛风。最后，果葡糖浆为液态摄入，更加隐蔽：容易在“喝”中超标果葡糖浆广泛存在于含糖饮料中，而液态糖的摄入速度极快，饱腹感却极弱。一项发表于《Metabolism》的临床研究对比了果葡糖浆饮料和白砂糖饮料，发现饮用果葡糖浆饮料后，血液中的果糖浓度峰值、尿酸上升幅度和收缩压最高值均显著高于白砂糖饮料组。（视频：北京卫视养生堂） #把配料表中的白砂糖还给我们# 新浪热点的微博视频</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>新浪热点</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 07:52:53</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:44:21</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>健康医疗</t>
         </is>
       </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="2" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Gumayusi女警一打四反杀</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>亚运会热身赛Gumayusi女警一打五玩成个人秀，真是神了#Gumayusi女警一打四反杀##LPL连续两年去S赛队伍一样# 竞圈风向标的微博视频</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>竞圈风向标</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 07:40:21</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:38:23</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>游戏</t>
         </is>
       </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>周也哭戏被嘲</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>周也这段哭戏感觉下一秒就要笑场了 冷玩A-ONE的微博视频</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>冷玩A-ONE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 21:46:11</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:34:21</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>剧集</t>
         </is>
       </c>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="n"/>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="2" t="n"/>
+      <c r="X7" s="2" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="72.5" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>闲鱼 涉黄</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>【#中新网评闲鱼暗藏涉黄产业链#：#闲鱼审核不能太闲了#】闲鱼又一次被推上了舆论的风口浪尖。据河北经视报道，闲鱼平台上至今仍暗藏涉黄产业链，记者在调查中发现，一些客服的个人信息中赫然写着“处宝可约”四个字，经进一步沟通确认，这些可供“预约”的女孩大多是未成年人，年龄最小的仅14岁。“处宝可约”四个字，是刺向未成年人保护底线的一根针。闲鱼可以“闲”，但审核不能闲，底线更不能闲。 中国新闻网的微博视频</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>中国新闻网</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 19:26:44</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 08:28:22</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>互联网</t>
         </is>
       </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>王俊凯妈妈给王俊凯庆生</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>#王俊凯妈妈给王俊凯庆生# 短片里好像看见王俊凯妈妈了 也一起祝王俊凯生日快乐🎂有家人的陪伴美美满满 还吹了两次蜡烛🎂#王俊凯过生日吹了两次蜡烛# 给我热一扎奶茶的微博视频</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>给我热一扎奶茶</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 01:33:27</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-09-21 07:21:18</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>艺人</t>
         </is>
       </c>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
